--- a/practice/HR_Absence_Sample.xlsx
+++ b/practice/HR_Absence_Sample.xlsx
@@ -2653,10 +2653,11 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Practice file for the JPS AI Productivity Workshop</t>
-        </is>
-      </c>
-    </row>
+          <t>Practice file for the AI Productivity Workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2667,7 +2668,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All names, codes and figures are fictional. Do not replace them with real JPS data.</t>
+          <t>All names, codes and figures are fictional. Do not replace them with real company data.</t>
         </is>
       </c>
     </row>
